--- a/BVSimulationFiles/74.xlsx
+++ b/BVSimulationFiles/74.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0007407407407407407</v>
+        <v>0.001481481481481481</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0007493564677459721</v>
+        <v>0.001498712935491944</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007577501308250983</v>
+        <v>0.001515500261650197</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007659250944652909</v>
+        <v>0.001531850188930582</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007738846799710696</v>
+        <v>0.001547769359942139</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007816321659747528</v>
+        <v>0.001563264331949506</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007891707889411681</v>
+        <v>0.001578341577882336</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000796503743666679</v>
+        <v>0.001593007487333358</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008036341837725932</v>
+        <v>0.001607268367545186</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008105652221930136</v>
+        <v>0.001621130444386027</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008172999316571929</v>
+        <v>0.001634599863314386</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008238413451664477</v>
+        <v>0.001647682690332895</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008301924564656986</v>
+        <v>0.001660384912931397</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0008363562205096869</v>
+        <v>0.001672712441019374</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008423355539239337</v>
+        <v>0.001684671107847867</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0008481333354604905</v>
+        <v>0.001696266670920981</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0008537524064485477</v>
+        <v>0.001707504812897095</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008591955712399478</v>
+        <v>0.001718391142479896</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008644655976496651</v>
+        <v>0.00172893119529933</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0008695652173913042</v>
+        <v>0.001739130434782608</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0007407407407407407</v>
+        <v>0.001481481481481481</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0007493564677459721</v>
+        <v>0.001498712935491944</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007577501308250983</v>
+        <v>0.001515500261650197</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007659250944652909</v>
+        <v>0.001531850188930582</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007738846799710696</v>
+        <v>0.001547769359942139</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007816321659747528</v>
+        <v>0.001563264331949506</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007891707889411681</v>
+        <v>0.001578341577882336</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000796503743666679</v>
+        <v>0.001593007487333358</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0008036341837725932</v>
+        <v>0.001607268367545186</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0008105652221930136</v>
+        <v>0.001621130444386027</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008172999316571929</v>
+        <v>0.001634599863314386</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0008238413451664477</v>
+        <v>0.001647682690332895</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008301924564656986</v>
+        <v>0.001660384912931397</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0008363562205096869</v>
+        <v>0.001672712441019374</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008423355539239337</v>
+        <v>0.001684671107847867</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008481333354604905</v>
+        <v>0.001696266670920981</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008537524064485477</v>
+        <v>0.001707504812897095</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008591955712399478</v>
+        <v>0.001718391142479896</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008644655976496651</v>
+        <v>0.00172893119529933</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0008695652173913042</v>
+        <v>0.001739130434782608</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/74.xlsx
+++ b/BVSimulationFiles/74.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001481481481481481</v>
+        <v>0.01481481481481481</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001498712935491944</v>
+        <v>0.01498712935491944</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001515500261650197</v>
+        <v>0.01515500261650197</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001531850188930582</v>
+        <v>0.01531850188930582</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001547769359942139</v>
+        <v>0.01547769359942139</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001563264331949506</v>
+        <v>0.01563264331949506</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001578341577882336</v>
+        <v>0.01578341577882336</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001593007487333358</v>
+        <v>0.01593007487333358</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001607268367545186</v>
+        <v>0.01607268367545186</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001621130444386027</v>
+        <v>0.01621130444386027</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001634599863314386</v>
+        <v>0.01634599863314386</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001647682690332895</v>
+        <v>0.01647682690332895</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001660384912931397</v>
+        <v>0.01660384912931397</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001672712441019374</v>
+        <v>0.01672712441019374</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001684671107847867</v>
+        <v>0.01684671107847867</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001696266670920981</v>
+        <v>0.01696266670920981</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001707504812897095</v>
+        <v>0.01707504812897095</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001718391142479896</v>
+        <v>0.01718391142479896</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00172893119529933</v>
+        <v>0.0172893119529933</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001739130434782608</v>
+        <v>0.01739130434782608</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001481481481481481</v>
+        <v>0.01481481481481481</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001498712935491944</v>
+        <v>0.01498712935491944</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001515500261650197</v>
+        <v>0.01515500261650197</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001531850188930582</v>
+        <v>0.01531850188930582</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001547769359942139</v>
+        <v>0.01547769359942139</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001563264331949506</v>
+        <v>0.01563264331949506</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001578341577882336</v>
+        <v>0.01578341577882336</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001593007487333358</v>
+        <v>0.01593007487333358</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001607268367545186</v>
+        <v>0.01607268367545186</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001621130444386027</v>
+        <v>0.01621130444386027</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001634599863314386</v>
+        <v>0.01634599863314386</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001647682690332895</v>
+        <v>0.01647682690332895</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001660384912931397</v>
+        <v>0.01660384912931397</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001672712441019374</v>
+        <v>0.01672712441019374</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001684671107847867</v>
+        <v>0.01684671107847867</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001696266670920981</v>
+        <v>0.01696266670920981</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001707504812897095</v>
+        <v>0.01707504812897095</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001718391142479896</v>
+        <v>0.01718391142479896</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00172893119529933</v>
+        <v>0.0172893119529933</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001739130434782608</v>
+        <v>0.01739130434782608</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/74.xlsx
+++ b/BVSimulationFiles/74.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01481481481481481</v>
+        <v>0.1746556302791719</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01498712935491944</v>
+        <v>0.1750567730353377</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01515500261650197</v>
+        <v>0.1753842452045744</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01531850188930582</v>
+        <v>0.1756406179629698</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01547769359942139</v>
+        <v>0.1758283928843239</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01563264331949506</v>
+        <v>0.1759500036296373</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01578341577882336</v>
+        <v>0.1760078175980172</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01593007487333358</v>
+        <v>0.1760041375398467</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01607268367545186</v>
+        <v>0.1759412031330475</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01621130444386027</v>
+        <v>0.175821192523248</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01634599863314386</v>
+        <v>0.1756462238286508</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01647682690332895</v>
+        <v>0.1754183566103747</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01660384912931397</v>
+        <v>0.1751395933090363</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01672712441019374</v>
+        <v>0.1748118806483102</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01684671107847867</v>
+        <v>0.1744371110062005</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01696266670920981</v>
+        <v>0.1740171237547333</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01707504812897095</v>
+        <v>0.1735537065687699</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01718391142479896</v>
+        <v>0.1730485967046204</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0172893119529933</v>
+        <v>0.1725034822491291</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01739130434782608</v>
+        <v>0.1719200033398815</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01481481481481481</v>
+        <v>0.1746556302791719</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01498712935491944</v>
+        <v>0.1750567730353377</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01515500261650197</v>
+        <v>0.1753842452045744</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01531850188930582</v>
+        <v>0.1756406179629698</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01547769359942139</v>
+        <v>0.1758283928843239</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01563264331949506</v>
+        <v>0.1759500036296373</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01578341577882336</v>
+        <v>0.1760078175980172</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01593007487333358</v>
+        <v>0.1760041375398467</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01607268367545186</v>
+        <v>0.1759412031330475</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01621130444386027</v>
+        <v>0.175821192523248</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01634599863314386</v>
+        <v>0.1756462238286508</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01647682690332895</v>
+        <v>0.1754183566103747</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01660384912931397</v>
+        <v>0.1751395933090363</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01672712441019374</v>
+        <v>0.1748118806483102</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01684671107847867</v>
+        <v>0.1744371110062005</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01696266670920981</v>
+        <v>0.1740171237547333</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01707504812897095</v>
+        <v>0.1735537065687699</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01718391142479896</v>
+        <v>0.1730485967046204</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0172893119529933</v>
+        <v>0.1725034822491291</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01739130434782608</v>
+        <v>0.1719200033398815</v>
       </c>
     </row>
   </sheetData>
